--- a/assets/data-source/calculator-data.xlsx
+++ b/assets/data-source/calculator-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venus\Desktop\PahnavarKar\assets\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF747BA-0004-4DFA-B520-3A3BBC5BE0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C3AE33-65B6-4807-B595-3B181D6F627A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="444" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -341,8 +341,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="165" formatCode="0.000;[Red]0.000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -745,7 +746,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -815,8 +816,41 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -845,41 +879,23 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1194,7 +1210,8 @@
     <col min="5" max="5" width="10.23046875" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.69140625" style="1"/>
     <col min="7" max="7" width="10" style="1"/>
-    <col min="8" max="9" width="11.69140625" style="1"/>
+    <col min="8" max="8" width="11.69140625" style="1"/>
+    <col min="9" max="9" width="11.69140625" style="49"/>
     <col min="10" max="10" width="10" style="1"/>
     <col min="11" max="12" width="11.69140625" style="1"/>
     <col min="13" max="13" width="11.69140625" style="2"/>
@@ -1215,80 +1232,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="72" customHeight="1" thickBot="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="35" t="s">
+      <c r="L1" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="42" t="s">
+      <c r="P1" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="37" t="s">
+      <c r="Q1" s="30"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="T1" s="38"/>
-      <c r="U1" s="37" t="s">
+      <c r="T1" s="34"/>
+      <c r="U1" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="V1" s="41"/>
-      <c r="W1" s="39" t="s">
+      <c r="V1" s="28"/>
+      <c r="W1" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="X1" s="33" t="s">
+      <c r="X1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="Y1" s="33" t="s">
+      <c r="Y1" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="Z1" s="39" t="s">
+      <c r="Z1" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="AA1" s="33" t="s">
+      <c r="AA1" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="AB1" s="33" t="s">
+      <c r="AB1" s="23" t="s">
         <v>96</v>
       </c>
       <c r="AE1" s="7"/>
@@ -1302,29 +1319,29 @@
       <c r="AM1" s="7"/>
     </row>
     <row r="2" spans="1:39" s="5" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="36" t="s">
+      <c r="L2" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
       <c r="P2" s="8" t="s">
         <v>102</v>
       </c>
@@ -1346,12 +1363,12 @@
       <c r="V2" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="W2" s="40"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="24"/>
       <c r="AE2" s="7"/>
       <c r="AF2" s="7"/>
       <c r="AG2" s="7"/>
@@ -1387,7 +1404,7 @@
       <c r="H3" s="11">
         <v>1000</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="46">
         <v>1</v>
       </c>
       <c r="J3" s="11">
@@ -1480,7 +1497,7 @@
       <c r="H4" s="11">
         <v>1667</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="46">
         <v>1</v>
       </c>
       <c r="J4" s="11">
@@ -1573,7 +1590,7 @@
       <c r="H5" s="11">
         <v>2267</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="46">
         <v>1</v>
       </c>
       <c r="J5" s="11">
@@ -1666,7 +1683,7 @@
       <c r="H6" s="11">
         <v>2994</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="46">
         <v>1.1000000000000001</v>
       </c>
       <c r="J6" s="11">
@@ -1759,7 +1776,7 @@
       <c r="H7" s="11">
         <v>3894</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="46">
         <v>1.1000000000000001</v>
       </c>
       <c r="J7" s="11">
@@ -1852,7 +1869,7 @@
       <c r="H8" s="11">
         <v>5333</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="46">
         <v>1.1000000000000001</v>
       </c>
       <c r="J8" s="11">
@@ -1945,7 +1962,7 @@
       <c r="H9" s="11">
         <v>6907</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="46">
         <v>1.228</v>
       </c>
       <c r="J9" s="11">
@@ -2038,7 +2055,7 @@
       <c r="H10" s="11">
         <v>8482</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="46">
         <v>1.07</v>
       </c>
       <c r="J10" s="11">
@@ -2122,7 +2139,7 @@
       <c r="H11" s="11">
         <v>10051</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="46">
         <v>1.1850000000000001</v>
       </c>
       <c r="J11" s="11">
@@ -2206,7 +2223,7 @@
       <c r="H12" s="11">
         <v>12061</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="46">
         <v>1.2</v>
       </c>
       <c r="J12" s="11">
@@ -2290,7 +2307,7 @@
       <c r="H13" s="11">
         <v>15267</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="46">
         <v>1.1000000000000001</v>
       </c>
       <c r="J13" s="11">
@@ -2374,7 +2391,7 @@
       <c r="H14" s="11">
         <v>18930</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="46">
         <v>1.05</v>
       </c>
       <c r="J14" s="11">
@@ -2458,7 +2475,7 @@
       <c r="H15" s="11">
         <v>23282</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="46">
         <v>1.0449999999999999</v>
       </c>
       <c r="J15" s="11">
@@ -2542,7 +2559,7 @@
       <c r="H16" s="11">
         <v>28446</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="46">
         <v>1.05</v>
       </c>
       <c r="J16" s="11">
@@ -2626,7 +2643,7 @@
       <c r="H17" s="11">
         <v>35534</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="46">
         <v>1</v>
       </c>
       <c r="J17" s="11">
@@ -2710,7 +2727,7 @@
       <c r="H18" s="11">
         <v>40864</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="46">
         <v>1</v>
       </c>
       <c r="J18" s="11">
@@ -2794,7 +2811,7 @@
       <c r="H19" s="11">
         <v>50000</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="46">
         <v>1.1000000000000001</v>
       </c>
       <c r="J19" s="11">
@@ -2878,7 +2895,7 @@
       <c r="H20" s="11">
         <v>61000</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="46">
         <v>1.1000000000000001</v>
       </c>
       <c r="J20" s="11">
@@ -2962,7 +2979,7 @@
       <c r="H21" s="11">
         <v>73200</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="46">
         <v>1.05</v>
       </c>
       <c r="J21" s="11">
@@ -3046,7 +3063,7 @@
       <c r="H22" s="11">
         <v>87840</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="46">
         <v>1.05</v>
       </c>
       <c r="J22" s="11">
@@ -3130,7 +3147,7 @@
       <c r="H23" s="11">
         <v>101000</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="46">
         <v>1.07</v>
       </c>
       <c r="J23" s="11">
@@ -3214,7 +3231,7 @@
       <c r="H24" s="11">
         <v>110100</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="46">
         <v>1.06</v>
       </c>
       <c r="J24" s="11">
@@ -3298,7 +3315,7 @@
       <c r="H25" s="11">
         <v>129900</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="46">
         <v>1.07</v>
       </c>
       <c r="J25" s="11">
@@ -3358,7 +3375,7 @@
       </c>
     </row>
     <row r="26" spans="1:28" ht="32.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A26" s="26">
+      <c r="A26" s="37">
         <v>1392</v>
       </c>
       <c r="B26" s="10">
@@ -3382,7 +3399,7 @@
       <c r="H26" s="11">
         <v>162375</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="46">
         <v>1.1000000000000001</v>
       </c>
       <c r="J26" s="22">
@@ -3437,12 +3454,12 @@
       <c r="AA26" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="AB26" s="26" t="s">
+      <c r="AB26" s="37" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="32.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A27" s="27"/>
+      <c r="A27" s="38"/>
       <c r="B27" s="10">
         <v>8</v>
       </c>
@@ -3464,7 +3481,7 @@
       <c r="H27" s="11">
         <v>162375</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="47">
         <v>1.1000000000000001</v>
       </c>
       <c r="J27" s="13">
@@ -3519,7 +3536,7 @@
       <c r="AA27" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="AB27" s="27"/>
+      <c r="AB27" s="38"/>
     </row>
     <row r="28" spans="1:28" ht="32.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A28" s="9">
@@ -3546,7 +3563,7 @@
       <c r="H28" s="11">
         <v>202970</v>
       </c>
-      <c r="I28" s="23">
+      <c r="I28" s="48">
         <v>1.1200000000000001</v>
       </c>
       <c r="J28" s="17">
@@ -3630,7 +3647,7 @@
       <c r="H29" s="12">
         <v>237475</v>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="48">
         <v>1.17</v>
       </c>
       <c r="J29" s="17">
@@ -3690,7 +3707,7 @@
       </c>
     </row>
     <row r="30" spans="1:28" ht="32.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A30" s="28">
+      <c r="A30" s="39">
         <v>1395</v>
       </c>
       <c r="B30" s="10">
@@ -3714,7 +3731,7 @@
       <c r="H30" s="12">
         <v>270722</v>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="48">
         <v>1.1399999999999999</v>
       </c>
       <c r="J30" s="17">
@@ -3769,12 +3786,12 @@
       <c r="AA30" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="AB30" s="32" t="s">
+      <c r="AB30" s="43" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="32.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A31" s="29"/>
+      <c r="A31" s="40"/>
       <c r="B31" s="10">
         <v>6</v>
       </c>
@@ -3796,7 +3813,7 @@
       <c r="H31" s="12">
         <v>270722</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="48">
         <v>1.1399999999999999</v>
       </c>
       <c r="J31" s="17">
@@ -3851,7 +3868,7 @@
       <c r="AA31" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="AB31" s="25"/>
+      <c r="AB31" s="36"/>
     </row>
     <row r="32" spans="1:28" ht="32.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A32" s="9">
@@ -3878,7 +3895,7 @@
       <c r="H32" s="12">
         <v>309977</v>
       </c>
-      <c r="I32" s="23">
+      <c r="I32" s="48">
         <v>1.1200000000000001</v>
       </c>
       <c r="J32" s="17">
@@ -3962,7 +3979,7 @@
       <c r="H33" s="11">
         <v>370423</v>
       </c>
-      <c r="I33" s="23">
+      <c r="I33" s="48">
         <v>1.1040000000000001</v>
       </c>
       <c r="J33" s="17">
@@ -4046,7 +4063,7 @@
       <c r="H34" s="11">
         <v>505627</v>
       </c>
-      <c r="I34" s="23">
+      <c r="I34" s="48">
         <v>1.1299999999999999</v>
       </c>
       <c r="J34" s="17">
@@ -4106,7 +4123,7 @@
       </c>
     </row>
     <row r="35" spans="1:39" ht="32.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A35" s="30">
+      <c r="A35" s="41">
         <v>1399</v>
       </c>
       <c r="B35" s="10">
@@ -4130,7 +4147,7 @@
       <c r="H35" s="11">
         <v>611809</v>
       </c>
-      <c r="I35" s="23">
+      <c r="I35" s="48">
         <v>1.1499999999999999</v>
       </c>
       <c r="J35" s="17">
@@ -4185,12 +4202,12 @@
       <c r="AA35" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="AB35" s="24" t="s">
+      <c r="AB35" s="35" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:39" ht="32.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A36" s="31"/>
+      <c r="A36" s="42"/>
       <c r="B36" s="10">
         <v>9</v>
       </c>
@@ -4212,7 +4229,7 @@
       <c r="H36" s="11">
         <v>636809</v>
       </c>
-      <c r="I36" s="23">
+      <c r="I36" s="48">
         <v>1.1499999999999999</v>
       </c>
       <c r="J36" s="17">
@@ -4267,7 +4284,7 @@
       <c r="AA36" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="AB36" s="25"/>
+      <c r="AB36" s="36"/>
     </row>
     <row r="37" spans="1:39" ht="32.25" customHeight="1" thickTop="1" thickBot="1">
       <c r="A37" s="9">
@@ -4294,7 +4311,7 @@
       <c r="H37" s="11">
         <v>885165</v>
       </c>
-      <c r="I37" s="23">
+      <c r="I37" s="48">
         <v>1.26</v>
       </c>
       <c r="J37" s="17">
@@ -4378,7 +4395,7 @@
       <c r="H38" s="11">
         <v>1393250</v>
       </c>
-      <c r="I38" s="23">
+      <c r="I38" s="48">
         <v>1.38</v>
       </c>
       <c r="J38" s="17">
@@ -4462,7 +4479,7 @@
       <c r="H39" s="11">
         <v>1769428</v>
       </c>
-      <c r="I39" s="23">
+      <c r="I39" s="48">
         <v>1.21</v>
       </c>
       <c r="J39" s="17">
@@ -4546,7 +4563,7 @@
       <c r="H40" s="11">
         <v>2388728</v>
       </c>
-      <c r="I40" s="23">
+      <c r="I40" s="48">
         <v>1.22</v>
       </c>
       <c r="J40" s="17">
@@ -4632,7 +4649,7 @@
       <c r="H41" s="11">
         <v>3463656</v>
       </c>
-      <c r="I41" s="23">
+      <c r="I41" s="48">
         <v>1.32</v>
       </c>
       <c r="J41" s="17">
@@ -4718,7 +4735,7 @@
       <c r="H42" s="11">
         <v>5541850</v>
       </c>
-      <c r="I42" s="23">
+      <c r="I42" s="48">
         <v>1.45</v>
       </c>
       <c r="J42" s="17">
@@ -7909,6 +7926,22 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AB35:AB36"/>
+    <mergeCell ref="AB26:AB27"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="AB30:AB31"/>
+    <mergeCell ref="AB1:AB2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="Z1:Z2"/>
     <mergeCell ref="D1:D2"/>
@@ -7923,22 +7956,6 @@
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="AB35:AB36"/>
-    <mergeCell ref="AB26:AB27"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="AB30:AB31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToWidth="0" fitToHeight="0"/>
